--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\CSTARS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7756065-6315-42B1-B02D-2BBD1C64FAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B92EAC-9656-497E-85E5-4ACF6BCC0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26265" yWindow="4485" windowWidth="29565" windowHeight="24570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27780" yWindow="5415" windowWidth="28455" windowHeight="24405" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="178">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -122,9 +122,6 @@
     <t>{ "PatientAction": { "Intubation": { "Type": "Tracheal" } } }</t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 5.0, "Unit": "min" }}}}</t>
-  </si>
-  <si>
     <t>Comparison Type</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>{ "PatientAction": { "Dyspnea": {
             "RespirationRateSeverity": { "Scalar0To1": { "Value": 0.0 } },
             "TidalVolumeSeverity": { "Scalar0To1": { "Value": 0.0 } } } } }</t>
-  </si>
-  <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 20.0, "Unit": "min" }}}}</t>
   </si>
   <si>
     <t>RespirationRate</t>
@@ -288,9 +282,6 @@
   </si>
   <si>
     <t>{ "PatientAction": { "Intubation": { "Type": "RightMainstem" } } }</t>
-  </si>
-  <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 10.0, "Unit": "min" }}}}</t>
   </si>
   <si>
     <t xml:space="preserve">The patient is agitated and PIP and Pplat have increased by 40%. SpO2 has fallen to 91% and ETCO2 has decreased to 31 mm Hg.  HR is 131 bpm and blood pressure is 118/76 mm Hg (MAP - 90 mm Hg) </t>
@@ -487,14 +478,6 @@
     <t>Suction patient.</t>
   </si>
   <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (delivered VT of 460 ml):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 22          | NA           | NA  | 1.3    | 16       | 5            | 0.40 |</t>
-  </si>
-  <si>
     <t>Remove plug.</t>
   </si>
   <si>
@@ -534,19 +517,6 @@
   <si>
     <t xml:space="preserve">Diagnosis: ETT plug.
 &lt;br /&gt; </t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } }
-  }}
-}</t>
   </si>
   <si>
     <t>HR</t>
@@ -769,37 +739,6 @@
 }</t>
   </si>
   <si>
-    <t>{ "PatientAction": { "Pneumonia":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 60.0, "Unit": "min" }}}}</t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Recognize moderate ARDS
- - Evaluate baseline ventilator settings
-Recommended Actions:
- - Reduce FiO2
-&lt;br /&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Objectives:
- - Recognize worsening ARDS (severe)
- - Adjust vent settings for safety
-Recommended Actions:
- - Note increase in ARDS severity (decreased P/F, increased PIP, Pplat, deltaP) - no vent changes
-</t>
-  </si>
-  <si>
-    <t>Moderate ARDS with Progressive Fall in Oxygenation</t>
-  </si>
-  <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
   "Mode": "AssistedControl", 
@@ -849,6 +788,58 @@
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
 | VC-CMV | 0.6    | NA          | 40           | NA  | 0.9    | 18      | 5            | 0.40 |</t>
+  </si>
+  <si>
+    <t>Mild ARDS with Progressive Fall in Oxygenation</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize mild ARDS
+ - Evaluate baseline ventilator settings
+Recommended Actions:
+ - Reduce FiO2
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Objectives:
+ - Recognize worsening ARDS (moderate)
+ - Adjust vent settings for safety
+Recommended Actions:
+ - Note increase in ARDS severity (decreased P/F, increased PIP, Pplat, deltaP) - no vent changes
+</t>
+  </si>
+  <si>
+    <t>{ "AdvanceUntilStable":  {} }</t>
+  </si>
+  <si>
+    <t>&lt;br /&gt;
+Ventilator settings are (delivered VT of 460 ml):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 22          | NA           | NA  | 1.3    | 10       | 5            | 0.40 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "PneumoniaExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
+  }}
+}</t>
   </si>
 </sst>
 </file>
@@ -917,7 +908,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -955,48 +946,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1052,25 +1006,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1080,6 +1016,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1480,44 +1425,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
       <c r="AMG1" s="14"/>
       <c r="AMH1" s="14"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
+      <c r="A2" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="27"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>109</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="AMG2" s="14"/>
       <c r="AMH2" s="14"/>
       <c r="AMI2" s="14"/>
@@ -1527,13 +1472,13 @@
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -1545,11 +1490,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -1568,12 +1513,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -1586,60 +1531,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1651,13 +1596,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>23</v>
@@ -1667,15 +1612,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1683,13 +1628,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>27</v>
@@ -1699,13 +1644,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1713,15 +1658,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1729,13 +1674,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -1750,13 +1695,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -1767,289 +1712,289 @@
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>8</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>11</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>52</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>108</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>140</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>76</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E24" s="2">
         <v>7.25</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>61</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2">
         <v>122</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E27" s="2">
         <v>0.98</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2">
         <v>51</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2">
         <v>244</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -2057,13 +2002,13 @@
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
       <c r="G30" s="1" t="s">
         <v>7</v>
       </c>
@@ -2075,15 +2020,15 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="B31" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H31" s="9"/>
     </row>
@@ -2091,15 +2036,15 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="B32" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -2107,13 +2052,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="21"/>
+      <c r="B33" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2128,13 +2073,13 @@
         <v>12</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>7</v>
@@ -2145,313 +2090,313 @@
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
         <v>28</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
         <v>12</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2">
         <v>14</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
         <v>35</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2">
         <v>115</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
         <v>136</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2">
         <v>76</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E42" s="2">
         <v>7.27</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2">
         <v>58</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="2">
         <v>91</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E45" s="2">
         <v>0.96</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2">
         <v>43</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="2">
         <v>182</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H47" s="10"/>
     </row>
@@ -2466,62 +2411,62 @@
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="2">
         <v>12.1</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G48" s="13"/>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E49" s="2">
         <v>1</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E50" s="2">
         <v>1</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H50" s="10"/>
     </row>
@@ -2529,13 +2474,13 @@
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
       <c r="G51" s="1" t="s">
         <v>7</v>
       </c>
@@ -2547,15 +2492,15 @@
       <c r="A52" s="8">
         <v>3</v>
       </c>
-      <c r="B52" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
+      <c r="B52" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
       <c r="G52" s="9" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2563,13 +2508,13 @@
       <c r="A53" s="8">
         <v>3</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
+      <c r="B53" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
       <c r="G53" s="9"/>
       <c r="H53" s="10"/>
     </row>
@@ -2584,13 +2529,13 @@
         <v>12</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>7</v>
@@ -2601,359 +2546,345 @@
     </row>
     <row r="55" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" s="2">
         <v>8</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" s="2">
         <v>11</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H56" s="10"/>
     </row>
     <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57" s="2">
         <v>49</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H57" s="10"/>
     </row>
     <row r="58" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" s="2">
         <v>116</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H58" s="10"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2">
         <v>139</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H59" s="10"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60" s="2">
         <v>78</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H60" s="10"/>
     </row>
     <row r="61" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E61" s="2">
         <v>7.39</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H61" s="10"/>
     </row>
     <row r="62" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62" s="2">
         <v>55</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H62" s="10"/>
     </row>
     <row r="63" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E63" s="2">
         <v>127</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H63" s="10"/>
     </row>
     <row r="64" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E64" s="2">
         <v>0.98</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H64" s="10"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E65" s="2">
         <v>30</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E66" s="2">
         <v>254</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H66" s="10"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E67" s="2">
         <v>2</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H67" s="10"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E68" s="2">
         <v>2</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H68" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B16:F16"/>
@@ -2962,9 +2893,23 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2993,42 +2938,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="AMI2" s="14"/>
       <c r="AMJ2" s="14"/>
     </row>
@@ -3036,13 +2981,13 @@
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -3054,11 +2999,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -3077,12 +3022,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -3095,60 +3040,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3160,13 +3105,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -3176,15 +3121,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3192,13 +3137,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3206,13 +3151,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3220,15 +3165,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3236,13 +3181,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -3257,13 +3202,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -3274,289 +3219,289 @@
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>18</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>18</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>48</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>79</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>150</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>83</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E24" s="2">
         <v>7.28</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>56</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2">
         <v>141</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E27" s="2">
         <v>0.99</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2">
         <v>38</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2">
         <v>282</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -3564,13 +3509,13 @@
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
       <c r="G30" s="1" t="s">
         <v>7</v>
       </c>
@@ -3582,15 +3527,15 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="B31" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H31" s="9"/>
     </row>
@@ -3598,27 +3543,27 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="B32" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="9"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
+      <c r="B33" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
       <c r="G33" s="9"/>
       <c r="H33" s="10"/>
     </row>
@@ -3633,13 +3578,13 @@
         <v>12</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>7</v>
@@ -3650,289 +3595,289 @@
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
         <v>25</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
         <v>25</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2">
         <v>53</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
         <v>99</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2">
         <v>145</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
         <v>90</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E41" s="2">
         <v>7.19</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" s="2">
         <v>70</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2">
         <v>148</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E44" s="2">
         <v>0.99</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" s="2">
         <v>56</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2">
         <v>296</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -3940,13 +3885,13 @@
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
       <c r="G47" s="1" t="s">
         <v>7</v>
       </c>
@@ -3958,15 +3903,15 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
+      <c r="B48" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
       <c r="G48" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -3974,13 +3919,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
+      <c r="B49" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
       <c r="G49" s="9"/>
       <c r="H49" s="10"/>
     </row>
@@ -3995,13 +3940,13 @@
         <v>12</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>7</v>
@@ -4012,300 +3957,308 @@
     </row>
     <row r="51" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51" s="2">
         <v>14</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2">
         <v>14</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53" s="2">
         <v>61</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" s="2">
         <v>103</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" s="2">
         <v>144</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" s="2">
         <v>91</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H56" s="10"/>
     </row>
     <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E57" s="2">
         <v>7.22</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H57" s="10"/>
     </row>
     <row r="58" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" s="2">
         <v>65</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H58" s="10"/>
     </row>
     <row r="59" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2">
         <v>151</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H59" s="10"/>
     </row>
     <row r="60" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E60" s="2">
         <v>0.99</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H60" s="10"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61" s="2">
         <v>68</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H61" s="10"/>
     </row>
     <row r="62" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E62" s="2">
         <v>302</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H62" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -4314,20 +4267,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4356,52 +4301,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>111</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -4413,11 +4358,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -4436,12 +4381,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4454,60 +4399,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -4519,13 +4464,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -4535,15 +4480,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -4551,13 +4496,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>27</v>
@@ -4567,13 +4512,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -4581,15 +4526,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4597,15 +4542,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -4620,13 +4565,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -4637,49 +4582,49 @@
     </row>
     <row r="18" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>102</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>130</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="14"/>
@@ -5701,25 +5646,25 @@
     </row>
     <row r="20" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>95</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="14"/>
@@ -6741,169 +6686,169 @@
     </row>
     <row r="21" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E21" s="2">
         <v>7.33</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>89</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E24" s="2">
         <v>0.92</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>178</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2">
         <v>34</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2">
         <v>30</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -6911,13 +6856,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -7945,15 +7890,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="B29" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="14"/>
@@ -8977,13 +8922,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="B30" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="9"/>
       <c r="H30" s="10"/>
       <c r="I30" s="14"/>
@@ -10007,15 +9952,15 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="B31" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="14"/>
@@ -11046,13 +10991,13 @@
         <v>12</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>7</v>
@@ -12079,25 +12024,25 @@
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>106</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="14"/>
@@ -13119,25 +13064,25 @@
     </row>
     <row r="34" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2">
         <v>140</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="14"/>
@@ -14159,25 +14104,25 @@
     </row>
     <row r="35" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
         <v>82</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="14"/>
@@ -15199,25 +15144,25 @@
     </row>
     <row r="36" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E36" s="2">
         <v>7.45</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="14"/>
@@ -16239,25 +16184,25 @@
     </row>
     <row r="37" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2">
         <v>35</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H37" s="10"/>
       <c r="I37" s="14"/>
@@ -17279,25 +17224,25 @@
     </row>
     <row r="38" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
         <v>57</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="14"/>
@@ -18319,25 +18264,25 @@
     </row>
     <row r="39" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E39" s="2">
         <v>0.87</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="14"/>
@@ -19359,25 +19304,25 @@
     </row>
     <row r="40" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
         <v>114</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="14"/>
@@ -20399,25 +20344,25 @@
     </row>
     <row r="41" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2">
         <v>39</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -21439,25 +21384,25 @@
     </row>
     <row r="42" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E42" s="2">
         <v>34</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H42" s="10"/>
       <c r="I42" s="14"/>
@@ -22481,13 +22426,13 @@
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
       <c r="G43" s="1" t="s">
         <v>7</v>
       </c>
@@ -23515,15 +23460,15 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
+      <c r="B44" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
       <c r="G44" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="14"/>
@@ -24547,13 +24492,13 @@
       <c r="A45" s="8">
         <v>3</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
+      <c r="B45" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
       <c r="G45" s="9"/>
       <c r="H45" s="10"/>
       <c r="I45" s="14"/>
@@ -25584,13 +25529,13 @@
         <v>12</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>7</v>
@@ -26617,25 +26562,25 @@
     </row>
     <row r="47" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="2">
         <v>102</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="14"/>
@@ -27657,25 +27602,25 @@
     </row>
     <row r="48" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E48" s="2">
         <v>7.33</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="14"/>
@@ -28697,25 +28642,25 @@
     </row>
     <row r="49" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="2">
         <v>49</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H49" s="10"/>
       <c r="I49" s="14"/>
@@ -29737,25 +29682,25 @@
     </row>
     <row r="50" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50" s="2">
         <v>57</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H50" s="10"/>
       <c r="I50" s="14"/>
@@ -30777,25 +30722,25 @@
     </row>
     <row r="51" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E51" s="2">
         <v>0.87</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="14"/>
@@ -31817,20 +31762,10 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B28:F28"/>
@@ -31841,10 +31776,20 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -31873,52 +31818,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>112</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -31930,11 +31875,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -31953,12 +31898,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -31971,60 +31916,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -32036,13 +31981,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -32052,15 +31997,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -32068,13 +32013,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>27</v>
@@ -32084,13 +32029,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -32098,15 +32043,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -32114,15 +32059,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -32137,13 +32082,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -32154,193 +32099,193 @@
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>94</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>118</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>69</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E21" s="2">
         <v>7.32</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>40</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>125</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E24" s="2">
         <v>0.98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>250</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -32348,13 +32293,13 @@
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
       <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
@@ -32366,15 +32311,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="B27" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -32382,15 +32327,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="B28" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -32405,13 +32350,13 @@
         <v>12</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>7</v>
@@ -32422,169 +32367,169 @@
     </row>
     <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2">
         <v>56</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2">
         <v>85</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>50</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E34" s="2">
         <v>0.83</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -32592,13 +32537,13 @@
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
       <c r="G37" s="1" t="s">
         <v>7</v>
       </c>
@@ -32610,15 +32555,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
+      <c r="B38" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
       <c r="G38" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -32626,13 +32571,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
+      <c r="B39" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -32647,13 +32592,13 @@
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>7</v>
@@ -32664,132 +32609,139 @@
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2">
         <v>106</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E42" s="2">
         <v>7.42</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2">
         <v>39</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="2">
         <v>140</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E45" s="2">
         <v>0.97</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -32798,19 +32750,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -32839,52 +32784,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>113</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -32896,11 +32841,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -32919,12 +32864,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -32937,60 +32882,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -33002,13 +32947,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -33018,15 +32963,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -33034,15 +32979,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>27</v>
@@ -33052,13 +32997,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -33066,15 +33011,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -33082,15 +33027,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -33105,13 +33050,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -33122,217 +33067,217 @@
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>109</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>133</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>84</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>100</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E22" s="2">
         <v>7.34</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>37</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
         <v>95</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E25" s="2">
         <v>0.94</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2">
         <v>190</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -33340,13 +33285,13 @@
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="1" t="s">
         <v>7</v>
       </c>
@@ -33358,15 +33303,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="B28" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -33374,15 +33319,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="B29" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -33397,13 +33342,13 @@
         <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>7</v>
@@ -33414,193 +33359,193 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2">
         <v>131</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2">
         <v>118</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>76</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2">
         <v>90</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E35" s="2">
         <v>0.91</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
         <v>31</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H36" s="18"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -33608,13 +33553,13 @@
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
       <c r="G39" s="1" t="s">
         <v>7</v>
       </c>
@@ -33626,15 +33571,15 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
       <c r="G40" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -33642,13 +33587,13 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="B41" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
       <c r="G41" s="9"/>
       <c r="H41" s="10"/>
     </row>
@@ -33663,13 +33608,13 @@
         <v>12</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>7</v>
@@ -33680,60 +33625,67 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2">
         <v>109</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E44" s="2">
         <v>0.96</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H44" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -33742,19 +33694,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -33783,52 +33728,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>114</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -33840,11 +33785,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -33863,12 +33808,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -33881,60 +33826,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -33946,13 +33891,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -33962,15 +33907,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -33978,15 +33923,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -33994,15 +33939,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="B14" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -34010,15 +33955,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -34033,13 +33978,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>7</v>
@@ -34050,265 +33995,265 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2">
         <v>520</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>20</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>114</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>138</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>79</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>100</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E23" s="2">
         <v>7.31</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
         <v>44</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>88</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E26" s="2">
         <v>0.95</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2">
         <v>147</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -34316,13 +34261,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -34334,15 +34279,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="B29" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -34350,15 +34295,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="B30" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -34373,13 +34318,13 @@
         <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>7</v>
@@ -34390,193 +34335,193 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2">
         <v>455</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H32" s="18"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>28</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2">
         <v>141</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
         <v>144</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
         <v>86</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2">
         <v>105</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E38" s="2">
         <v>0.9</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2">
         <v>45</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H39" s="18"/>
     </row>
@@ -34584,13 +34529,13 @@
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
       <c r="G40" s="1" t="s">
         <v>7</v>
       </c>
@@ -34602,15 +34547,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="B41" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
       <c r="G41" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -34618,13 +34563,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
+      <c r="B42" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
@@ -34639,13 +34584,13 @@
         <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>7</v>
@@ -34656,60 +34601,66 @@
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E44" s="2">
         <v>114</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E45" s="2">
         <v>0.96</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -34718,18 +34669,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -34758,52 +34703,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="A2" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="21"/>
       <c r="E2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+        <v>115</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -34815,11 +34760,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -34838,12 +34783,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -34856,60 +34801,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -34921,13 +34866,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -34937,15 +34882,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
+      <c r="B12" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -34953,15 +34898,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -34969,15 +34914,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="B14" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="9" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -34985,15 +34930,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="B15" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -35008,13 +34953,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>7</v>
@@ -35025,265 +34970,265 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2">
         <v>460</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2">
         <v>22</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <v>91</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2">
         <v>151</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2">
         <v>85</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2">
         <v>106</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E23" s="2">
         <v>7.39</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
         <v>47</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2">
         <v>97</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E26" s="2">
         <v>0.99</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2">
         <v>242</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -35291,13 +35236,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -35309,13 +35254,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10" t="s">
         <v>25</v>
@@ -35325,15 +35270,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="B30" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -35341,15 +35286,15 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="B31" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -35364,13 +35309,13 @@
         <v>12</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>7</v>
@@ -35381,193 +35326,193 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>60</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H33" s="18"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2">
         <v>40</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2">
         <v>141</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" s="2">
         <v>144</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2">
         <v>86</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
         <v>105</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E39" s="2">
         <v>0.85</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
         <v>45</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H40" s="18"/>
     </row>
@@ -35575,13 +35520,13 @@
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
       <c r="G41" s="1" t="s">
         <v>7</v>
       </c>
@@ -35593,15 +35538,15 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
+      <c r="B42" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
       <c r="G42" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -35609,13 +35554,13 @@
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
+      <c r="B43" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
       <c r="G43" s="9"/>
       <c r="H43" s="10"/>
     </row>
@@ -35630,13 +35575,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>7</v>
@@ -35647,60 +35592,67 @@
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" s="2">
         <v>91</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E46" s="2">
         <v>0.95</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H46" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -35709,19 +35661,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B92EAC-9656-497E-85E5-4ACF6BCC0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649538A5-929B-47F0-954D-1BB634B0E5FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27780" yWindow="5415" windowWidth="28455" windowHeight="24405" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29205" yWindow="4410" windowWidth="28230" windowHeight="25455" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Scenario6" sheetId="6" r:id="rId6"/>
     <sheet name="Scenario7" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -739,57 +739,6 @@
 }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 40, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.9, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 18, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 600, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Change in ventilator settings.
-Learning Objectives:
- - Recognize and address fall in oxygenation
- - Recognize and if required - address increase in PIP to maintain lung protection. (Pplat &lt; 30 cm H2O) (reduce VT)
- - Increase PEEP (first choice) and/or FIO2
-Recommended Actions:
- - Decrease FiO2 until SpO2 acceptable
- - Then match PEEP to FiO2
- - Decrease tidal volume to get Pplat &lt; 30
-Ventilator settings are updated to:
- - PEEP: 8 -&gt; 14 cmH2O
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.6    | NA          | 40           | NA  | 0.9    | 18      | 15            | 0.40 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 40, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.9, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 18, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 600, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.6    | NA          | 40           | NA  | 0.9    | 18      | 5            | 0.40 |</t>
-  </si>
-  <si>
     <t>Mild ARDS with Progressive Fall in Oxygenation</t>
   </si>
   <si>
@@ -840,6 +789,57 @@
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
   }}
 }</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Change in ventilator settings.
+Learning Objectives:
+ - Recognize and address fall in oxygenation
+ - Recognize and if required - address increase in PIP to maintain lung protection. (Pplat &lt; 30 cm H2O) (reduce VT)
+ - Increase PEEP (first choice) and/or FIO2
+Recommended Actions:
+ - Decrease FiO2 until SpO2 acceptable
+ - Then match PEEP to FiO2
+ - Decrease tidal volume to get Pplat &lt; 30
+Ventilator settings are updated to:
+ - PEEP: 8 -&gt; 14 cmH2O
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 15            | 0.4 |</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1448,7 @@
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21" t="s">
@@ -1620,7 +1620,7 @@
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
       <c r="G12" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1659,14 +1659,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
       <c r="G15" s="9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -2044,7 +2044,7 @@
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
       <c r="G32" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -2053,7 +2053,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -2493,14 +2493,14 @@
         <v>3</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
       <c r="E52" s="25"/>
       <c r="F52" s="25"/>
       <c r="G52" s="9" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -3558,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
@@ -3920,7 +3920,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
@@ -4543,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -9953,7 +9953,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -24493,7 +24493,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -31770,12 +31770,12 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B29:F29"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -32060,7 +32060,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -32328,7 +32328,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
@@ -32572,7 +32572,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
@@ -33028,7 +33028,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
@@ -33320,7 +33320,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
@@ -33588,7 +33588,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
@@ -33908,7 +33908,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -33956,7 +33956,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -34296,7 +34296,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -34564,7 +34564,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
@@ -34915,14 +34915,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
       <c r="G14" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -34931,7 +34931,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -35287,7 +35287,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
@@ -35555,7 +35555,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53130089-3FFD-4B39-BCA8-872C439722F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA34990-8763-4954-BA3E-4B96B4BA0860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="17250" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Scenario6" sheetId="6" r:id="rId7"/>
     <sheet name="Scenario7" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="319">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>{ "PatientAction": { "Intubation": { "Type": "Tracheal" } } }</t>
-  </si>
-  <si>
-    <t>Comparison Segment/Value</t>
   </si>
   <si>
     <t>Reference</t>
@@ -1176,9 +1173,6 @@
   </si>
   <si>
     <t>{v} = 488</t>
-  </si>
-  <si>
-    <t>ComparisonFormula</t>
   </si>
   <si>
     <t>CSTARS/Patient7.json</t>
@@ -1862,63 +1856,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1952,15 +1889,6 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,6 +1915,72 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2376,392 +2370,392 @@
   <dimension ref="A1:AD26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="50.5703125" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="15.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="9" max="30" width="9.140625" style="57"/>
+    <col min="1" max="1" width="50.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="15.85546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="9" max="30" width="9.140625" style="35"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="41"/>
-      <c r="B1" s="46" t="s">
+      <c r="A1" s="22"/>
+      <c r="B1" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="C2" s="49" t="s">
-        <v>315</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="E2" s="49" t="s">
-        <v>317</v>
-      </c>
-      <c r="F2" s="49" t="s">
-        <v>318</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>319</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="E4" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="43" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B6" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="C4" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="D4" s="53" t="s">
+      <c r="C6" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="E4" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>295</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>294</v>
-      </c>
-      <c r="H4" s="53" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
+      <c r="D6" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="B7" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>296</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>297</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>298</v>
-      </c>
-      <c r="E6" s="55" t="s">
-        <v>298</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="G6" s="55" t="s">
-        <v>300</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+      <c r="B8" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="B7" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>304</v>
-      </c>
-      <c r="E7" s="55" t="s">
-        <v>304</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>305</v>
-      </c>
-      <c r="G7" s="55" t="s">
-        <v>306</v>
-      </c>
-      <c r="H7" s="56" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>308</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>309</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>310</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>309</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>311</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>312</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="30"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="41" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="52"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="44" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="56"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="44" t="s">
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="34"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="56"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="44" t="s">
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="34"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="44" t="s">
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="34"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="44" t="s">
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="56"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="44" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="56"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="45" t="s">
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="56"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="44" t="s">
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="56"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="44" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="56"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="41" t="s">
+      <c r="B22" s="32"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="52"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="44" t="s">
+      <c r="B23" s="32"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="34"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="44" t="s">
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="34"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="56"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="44" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="34"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="56"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="56"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="56"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2789,42 +2783,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>246</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2834,13 +2828,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2852,13 +2846,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2875,74 +2869,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2954,13 +2948,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>22</v>
@@ -2970,15 +2964,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2986,13 +2980,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>24</v>
@@ -3002,13 +2996,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3016,15 +3010,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="48"/>
       <c r="G15" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3032,13 +3026,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3053,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3070,167 +3064,167 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>80</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>81</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>82</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>83</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="36"/>
+        <v>84</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24" s="36"/>
+        <v>85</v>
+      </c>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -3242,13 +3236,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -3256,15 +3250,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -3272,15 +3266,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -3288,13 +3282,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -3302,13 +3296,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
@@ -3323,13 +3317,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -3340,167 +3334,167 @@
     </row>
     <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="36"/>
+        <v>87</v>
+      </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H34" s="36"/>
+        <v>88</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" s="36"/>
+        <v>89</v>
+      </c>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H36" s="36"/>
+        <v>90</v>
+      </c>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" s="36"/>
+        <v>91</v>
+      </c>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H38" s="36"/>
+        <v>177</v>
+      </c>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -3512,13 +3506,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -3526,31 +3520,31 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="48"/>
       <c r="G41" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H41" s="36"/>
+        <v>200</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
+      <c r="B42" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="36"/>
+      <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
@@ -3563,13 +3557,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>6</v>
@@ -3580,79 +3574,79 @@
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H44" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46" s="36"/>
+        <v>76</v>
+      </c>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -3664,29 +3658,29 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="19"/>
+      <c r="B48" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="48"/>
       <c r="G48" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="H48" s="36"/>
+        <v>202</v>
+      </c>
+      <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
+      <c r="B49" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
@@ -3694,15 +3688,15 @@
       <c r="A50" s="8">
         <v>4</v>
       </c>
-      <c r="B50" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="19"/>
+      <c r="B50" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="48"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="36"/>
+      <c r="H50" s="17"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -3715,13 +3709,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3732,147 +3726,139 @@
     </row>
     <row r="52" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H52" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H52" s="17"/>
     </row>
     <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H53" s="36"/>
+        <v>58</v>
+      </c>
+      <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H54" s="36"/>
+        <v>61</v>
+      </c>
+      <c r="H54" s="17"/>
     </row>
     <row r="55" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H55" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H55" s="17"/>
     </row>
     <row r="56" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H56" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="H56" s="17"/>
     </row>
     <row r="57" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H57" s="36"/>
+        <v>76</v>
+      </c>
+      <c r="H57" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
@@ -3884,6 +3870,17 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B14:F14"/>
@@ -3895,9 +3892,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3926,40 +3920,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>245</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -3967,13 +3961,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3985,13 +3979,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4008,14 +4002,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4028,60 +4022,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4093,15 +4087,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4109,75 +4103,75 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="36"/>
+        <v>110</v>
+      </c>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:1024" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="36"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:1024" ht="219" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="36"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
@@ -4190,13 +4184,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4207,145 +4201,145 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>99</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>100</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>101</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>102</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="36"/>
+        <v>103</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4357,13 +4351,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -4371,15 +4365,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
       <c r="G26" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -4387,13 +4381,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
+      <c r="B27" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="57"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -4401,13 +4395,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -4415,15 +4409,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="36"/>
+      <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
@@ -4436,13 +4430,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -4453,123 +4447,123 @@
     </row>
     <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H33" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H35" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4581,13 +4575,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -4595,29 +4589,29 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
+      <c r="B38" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="48"/>
       <c r="G38" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="H38" s="36"/>
+        <v>209</v>
+      </c>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -4625,15 +4619,15 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
       <c r="G40" s="9"/>
-      <c r="H40" s="36"/>
+      <c r="H40" s="17"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
@@ -4646,13 +4640,13 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>6</v>
@@ -4663,135 +4657,114 @@
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H42" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H44" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H45" s="17"/>
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H46" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -4804,6 +4777,27 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4832,50 +4826,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>244</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4887,13 +4881,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4910,14 +4904,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4930,61 +4924,61 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="37" t="s">
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H10" s="6" t="s">
@@ -4995,15 +4989,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="36" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5011,47 +5005,47 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="36" t="s">
-        <v>181</v>
+      <c r="B12" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="H13" s="36"/>
+      <c r="B13" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="36" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="17" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5059,45 +5053,45 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="36"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" ht="215.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="38" t="s">
+      <c r="B16" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:1024" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="36"/>
+      <c r="B17" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
@@ -5110,15 +5104,15 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -5127,168 +5121,168 @@
     </row>
     <row r="19" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
-      <c r="G19" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="36"/>
+      <c r="G19" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
-      <c r="G20" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="36"/>
+      <c r="G20" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
-      <c r="G21" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="36"/>
+      <c r="G21" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="10"/>
-      <c r="G22" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="36"/>
+      <c r="G22" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" s="10"/>
-      <c r="G23" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="36"/>
+      <c r="G23" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F24" s="10"/>
-      <c r="G24" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="36"/>
+      <c r="G24" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="F25" s="10"/>
-      <c r="G25" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="36"/>
+      <c r="G25" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="37" t="s">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H26" s="6" t="s">
@@ -6315,31 +6309,31 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="38"/>
+      <c r="B27" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:1024" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" s="36"/>
+      <c r="B28" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="17"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
@@ -7361,16 +7355,16 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="36" t="s">
-        <v>195</v>
+      <c r="B29" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
@@ -8393,17 +8387,17 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="H30" s="36"/>
+      <c r="B30" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="17"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
@@ -9425,28 +9419,28 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="38"/>
+      <c r="B31" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="H32" s="36"/>
+      <c r="B32" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="H32" s="17"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
@@ -10475,15 +10469,15 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G33" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H33" s="6" t="s">
@@ -11508,168 +11502,168 @@
     </row>
     <row r="34" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
-      <c r="G34" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="36"/>
+      <c r="G34" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="10"/>
-      <c r="G35" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="H35" s="36"/>
+      <c r="G35" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="10"/>
-      <c r="G36" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H36" s="36"/>
+      <c r="G36" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F37" s="10"/>
-      <c r="G37" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="H37" s="36"/>
+      <c r="G37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F38" s="10"/>
-      <c r="G38" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="H38" s="36"/>
+      <c r="G38" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F39" s="10"/>
-      <c r="G39" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="H39" s="36"/>
+      <c r="G39" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F40" s="10"/>
-      <c r="G40" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="H40" s="36"/>
+      <c r="G40" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H40" s="17"/>
     </row>
     <row r="41" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="37" t="s">
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H41" s="6" t="s">
@@ -12696,31 +12690,31 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="38"/>
+      <c r="B42" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="19"/>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:1024" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="38" t="s">
+      <c r="B43" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="H43" s="36"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" s="17"/>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
       <c r="K43" s="13"/>
@@ -13742,15 +13736,15 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="36"/>
+      <c r="B44" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="17"/>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
       <c r="K44" s="13"/>
@@ -14779,15 +14773,15 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G45" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G45" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H45" s="6" t="s">
@@ -15812,58 +15806,58 @@
     </row>
     <row r="46" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
-      <c r="G46" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H46" s="36"/>
+      <c r="G46" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F47" s="10"/>
-      <c r="G47" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H47" s="36"/>
+      <c r="G47" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" s="17"/>
     </row>
     <row r="48" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="37" t="s">
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -16890,17 +16884,17 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="H49" s="36"/>
+      <c r="B49" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="H49" s="17"/>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
       <c r="K49" s="13"/>
@@ -17922,29 +17916,29 @@
       <c r="A50" s="8">
         <v>4</v>
       </c>
-      <c r="B50" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="38"/>
+      <c r="B50" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="19"/>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>4</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="36"/>
+      <c r="B51" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="17"/>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
       <c r="K51" s="13"/>
@@ -18973,15 +18967,15 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G52" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G52" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H52" s="6" t="s">
@@ -20006,70 +20000,48 @@
     </row>
     <row r="53" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
-      <c r="G53" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H53" s="36"/>
+      <c r="G53" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H53" s="17"/>
     </row>
     <row r="54" spans="1:1024" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F54" s="10"/>
-      <c r="G54" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H54" s="36"/>
+      <c r="G54" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B16:F16"/>
@@ -20086,6 +20058,28 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20114,50 +20108,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>243</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20169,13 +20163,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -20192,14 +20186,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20212,60 +20206,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20277,15 +20271,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -20293,47 +20287,47 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="36" t="s">
-        <v>181</v>
+      <c r="H12" s="17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="36"/>
+        <v>165</v>
+      </c>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="36" t="s">
+      <c r="H14" s="17" t="s">
         <v>24</v>
       </c>
     </row>
@@ -20341,45 +20335,45 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" ht="208.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48"/>
       <c r="G16" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="H16" s="36"/>
+        <v>189</v>
+      </c>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
+      <c r="B17" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="36"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
@@ -20392,13 +20386,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -20409,167 +20403,167 @@
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>87</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>88</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>89</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="36"/>
+        <v>90</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="36"/>
+        <v>91</v>
+      </c>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -20581,13 +20575,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -20595,29 +20589,29 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H28" s="36"/>
+        <v>185</v>
+      </c>
+      <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -20625,17 +20619,17 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="B30" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
       <c r="G30" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="H30" s="36"/>
+        <v>186</v>
+      </c>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -20648,13 +20642,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -20665,167 +20659,167 @@
     </row>
     <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H33" s="36"/>
+        <v>58</v>
+      </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H34" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="H35" s="17"/>
     </row>
     <row r="36" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H36" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H38" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -20837,13 +20831,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -20851,47 +20845,47 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
+      <c r="B41" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
       <c r="G41" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H41" s="36"/>
+        <v>139</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" ht="171.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="36" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
+      <c r="B43" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
@@ -20899,15 +20893,15 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
+      <c r="B44" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="36"/>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -20920,13 +20914,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>6</v>
@@ -20937,179 +20931,158 @@
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H46" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H47" s="36"/>
+        <v>58</v>
+      </c>
+      <c r="H47" s="17"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H48" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H49" s="36"/>
+        <v>60</v>
+      </c>
+      <c r="H49" s="17"/>
     </row>
     <row r="50" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H50" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H50" s="17"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H51" s="17"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H52" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
@@ -21123,6 +21096,27 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21151,50 +21145,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>242</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21206,13 +21200,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -21229,14 +21223,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21249,60 +21243,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21314,15 +21308,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -21330,61 +21324,61 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="36"/>
+        <v>165</v>
+      </c>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="215.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48"/>
       <c r="G14" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="36"/>
+        <v>162</v>
+      </c>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -21397,13 +21391,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -21414,167 +21408,167 @@
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H18" s="36"/>
+        <v>87</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>88</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>89</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>90</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>91</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="36"/>
+        <v>77</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -21586,13 +21580,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -21600,29 +21594,29 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
       <c r="G26" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H26" s="36"/>
+        <v>140</v>
+      </c>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -21630,17 +21624,17 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H28" s="36"/>
+        <v>217</v>
+      </c>
+      <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
@@ -21653,13 +21647,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>6</v>
@@ -21670,123 +21664,123 @@
     </row>
     <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H30" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="36"/>
+        <v>58</v>
+      </c>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H33" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -21798,13 +21792,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
     </row>
@@ -21812,29 +21806,29 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="H37" s="36"/>
+        <v>218</v>
+      </c>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
@@ -21842,17 +21836,17 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
+      <c r="B39" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
       <c r="G39" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="H39" s="36"/>
+        <v>219</v>
+      </c>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -21865,13 +21859,13 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>6</v>
@@ -21882,135 +21876,114 @@
     </row>
     <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H41" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H42" s="36"/>
+        <v>58</v>
+      </c>
+      <c r="H42" s="17"/>
     </row>
     <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H43" s="36"/>
+        <v>62</v>
+      </c>
+      <c r="H43" s="17"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" s="36"/>
+        <v>65</v>
+      </c>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H45" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
@@ -22021,6 +21994,27 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22049,50 +22043,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>241</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22104,13 +22098,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -22127,14 +22121,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22147,60 +22141,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22212,15 +22206,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -22228,29 +22222,29 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="36"/>
+        <v>165</v>
+      </c>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
     </row>
@@ -22258,31 +22252,31 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48"/>
       <c r="G14" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H14" s="36"/>
+        <v>215</v>
+      </c>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="B15" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -22295,13 +22289,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -22312,147 +22306,147 @@
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="36"/>
+        <v>87</v>
+      </c>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="36"/>
+        <v>88</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>89</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>90</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>91</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>177</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -22464,13 +22458,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
     </row>
@@ -22478,29 +22472,29 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="B25" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="36"/>
+        <v>187</v>
+      </c>
+      <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -22508,17 +22502,17 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H27" s="36"/>
+        <v>141</v>
+      </c>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
@@ -22531,13 +22525,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>6</v>
@@ -22548,79 +22542,79 @@
     </row>
     <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H30" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H31" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
       <c r="G32" s="1" t="s">
         <v>6</v>
       </c>
@@ -22632,13 +22626,13 @@
       <c r="A33" s="8">
         <v>3</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
+      <c r="B33" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -22646,29 +22640,29 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
       <c r="G34" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="36"/>
+        <v>142</v>
+      </c>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -22676,17 +22670,17 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
+      <c r="B36" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="48"/>
       <c r="G36" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H36" s="36"/>
+        <v>167</v>
+      </c>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
@@ -22699,13 +22693,13 @@
         <v>11</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>6</v>
@@ -22716,91 +22710,70 @@
     </row>
     <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H40" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H40" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B23:F23"/>
@@ -22811,6 +22784,27 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22839,50 +22833,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="A2" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>240</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22894,13 +22888,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -22917,14 +22911,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="20"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22937,60 +22931,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -23002,15 +22996,15 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -23018,77 +23012,77 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="36" t="s">
-        <v>181</v>
+      <c r="H12" s="17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
       <c r="G13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H13" s="36"/>
+        <v>144</v>
+      </c>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="36"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
+      <c r="B16" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="36"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
@@ -23101,13 +23095,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -23118,167 +23112,167 @@
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="36"/>
+        <v>80</v>
+      </c>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="36"/>
+        <v>81</v>
+      </c>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="36"/>
+        <v>82</v>
+      </c>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="36"/>
+        <v>83</v>
+      </c>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="36"/>
+        <v>84</v>
+      </c>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H24" s="36"/>
+        <v>85</v>
+      </c>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -23290,13 +23284,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B26" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -23304,29 +23298,29 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
       <c r="G27" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="36"/>
+        <v>188</v>
+      </c>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="B28" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -23334,17 +23328,17 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="B29" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
       <c r="G29" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H29" s="36"/>
+        <v>145</v>
+      </c>
+      <c r="H29" s="17"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
@@ -23357,13 +23351,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -23374,79 +23368,79 @@
     </row>
     <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H33" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -23458,13 +23452,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
+      <c r="B35" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -23472,29 +23466,29 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
+      <c r="B36" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
       <c r="G36" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="H36" s="36"/>
+        <v>146</v>
+      </c>
+      <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -23502,19 +23496,19 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H38" s="36"/>
-    </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
@@ -23525,13 +23519,13 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>6</v>
@@ -23542,91 +23536,70 @@
     </row>
     <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H40" s="36"/>
+        <v>98</v>
+      </c>
+      <c r="H40" s="17"/>
     </row>
     <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="36"/>
+        <v>56</v>
+      </c>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H42" s="36"/>
+        <v>57</v>
+      </c>
+      <c r="H42" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
@@ -23638,6 +23611,27 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA34990-8763-4954-BA3E-4B96B4BA0860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1064172-0534-42E0-85F8-B520AA5C648A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Scenario6" sheetId="6" r:id="rId7"/>
     <sheet name="Scenario7" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -236,15 +236,6 @@
     <t>Hypoxemic Respiratory Failure Plugged ETT</t>
   </si>
   <si>
-    <t>{ "PatientAction": {
-      "AirwayObstruction": {
-        "Severity": {
-          "Scalar0To1": {
-            "Value": 0.5
-          } } } }
-  }</t>
-  </si>
-  <si>
     <t>Rinsp</t>
   </si>
   <si>
@@ -760,15 +751,6 @@
     <t>PaO2/FiO2 for moderate ARDS</t>
   </si>
   <si>
-    <t>{ "PatientAction": { "PneumoniaExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
-  }}
-}</t>
-  </si>
-  <si>
     <t>Twenty minutes into the transport the patient is slightly agitated and is making inspiratory efforts that are not in sync with the ventilator.
 Learning Objectives:
  - Recognize increased airway resistance (PIP much higher than Pplat)
@@ -1411,6 +1393,24 @@
   </si>
   <si>
     <t>Patient7</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "PneumoniaExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.29 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.29 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": {
+      "AirwayObstruction": {
+        "Severity": {
+          "Scalar0To1": {
+            "Value": 0.4
+          } } } }
+  }</t>
   </si>
 </sst>
 </file>
@@ -1925,6 +1925,27 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1943,12 +1964,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1957,21 +1972,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2378,7 +2378,7 @@
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
@@ -2389,33 +2389,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="E2" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="F2" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="G2" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="H2" s="27" t="s">
         <v>316</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
@@ -2427,33 +2427,33 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
@@ -2465,85 +2465,85 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B6" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="E6" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="G6" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="H6" s="34" t="s">
         <v>297</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B7" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="E7" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="G7" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="H7" s="34" t="s">
         <v>303</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B8" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="E8" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="G8" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="H8" s="34" t="s">
         <v>309</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="33"/>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33"/>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33"/>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="33"/>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="33"/>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33"/>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="33"/>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29"/>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="33"/>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="33"/>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="33"/>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="33"/>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33"/>
@@ -2783,42 +2783,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="A2" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>244</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2828,13 +2828,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2846,11 +2846,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -2869,74 +2869,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2948,13 +2948,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>22</v>
@@ -2964,15 +2964,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
+      <c r="B12" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2980,13 +2980,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>24</v>
@@ -2996,13 +2996,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3010,15 +3010,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48"/>
+      <c r="B15" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3026,13 +3026,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="B16" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3047,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3073,12 +3073,12 @@
         <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -3087,20 +3087,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -3109,20 +3109,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -3131,20 +3131,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -3153,20 +3153,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3175,20 +3175,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3203,14 +3203,14 @@
         <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3218,13 +3218,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -3236,13 +3236,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
+      <c r="B26" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -3250,15 +3250,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -3266,15 +3266,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="B28" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -3282,13 +3282,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="B29" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -3296,13 +3296,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="B30" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
@@ -3317,13 +3317,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -3343,12 +3343,12 @@
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -3357,20 +3357,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -3379,20 +3379,20 @@
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -3401,20 +3401,20 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -3423,20 +3423,20 @@
         <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -3445,20 +3445,20 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -3473,14 +3473,14 @@
         <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3488,13 +3488,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -3506,13 +3506,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="B40" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -3520,15 +3520,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="45" t="s">
-        <v>201</v>
-      </c>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="48"/>
+      <c r="B41" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="53"/>
       <c r="G41" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -3536,13 +3536,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
+      <c r="B42" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="9"/>
       <c r="H42" s="17"/>
     </row>
@@ -3557,13 +3557,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>6</v>
@@ -3583,12 +3583,12 @@
         <v>52</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -3603,14 +3603,14 @@
         <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H45" s="17"/>
     </row>
@@ -3619,20 +3619,20 @@
         <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -3640,13 +3640,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -3658,15 +3658,15 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="48"/>
+      <c r="B48" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="53"/>
       <c r="G48" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -3674,13 +3674,13 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
+      <c r="B49" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
@@ -3688,13 +3688,13 @@
       <c r="A50" s="8">
         <v>4</v>
       </c>
-      <c r="B50" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="48"/>
+      <c r="B50" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53"/>
       <c r="G50" s="9"/>
       <c r="H50" s="17"/>
     </row>
@@ -3709,13 +3709,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3735,12 +3735,12 @@
         <v>52</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H52" s="17"/>
     </row>
@@ -3749,20 +3749,20 @@
         <v>27</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -3777,14 +3777,14 @@
         <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H54" s="17"/>
     </row>
@@ -3799,14 +3799,14 @@
         <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H55" s="17"/>
     </row>
@@ -3821,14 +3821,14 @@
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H56" s="17"/>
     </row>
@@ -3837,46 +3837,25 @@
         <v>27</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H57" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="G6:H9"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
@@ -3892,6 +3871,27 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3920,40 +3920,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>243</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -3961,13 +3961,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3979,11 +3979,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -4002,14 +4002,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4022,60 +4022,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4087,13 +4087,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -4103,15 +4103,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
+      <c r="B12" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4119,13 +4119,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
     </row>
@@ -4133,13 +4133,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17"/>
     </row>
@@ -4147,15 +4147,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="B15" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -4163,13 +4163,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="B16" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="9"/>
       <c r="H16" s="17"/>
     </row>
@@ -4184,13 +4184,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4210,12 +4210,12 @@
         <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -4224,20 +4224,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -4246,20 +4246,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -4268,20 +4268,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -4290,20 +4290,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4312,20 +4312,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -4333,13 +4333,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4351,13 +4351,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="B25" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -4365,15 +4365,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
+      <c r="B26" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -4395,13 +4395,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="B28" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -4409,13 +4409,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="B29" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9"/>
       <c r="H29" s="17"/>
     </row>
@@ -4430,13 +4430,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -4456,12 +4456,12 @@
         <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -4470,20 +4470,20 @@
         <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -4492,20 +4492,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -4520,14 +4520,14 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -4542,14 +4542,14 @@
         <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -4557,13 +4557,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4575,13 +4575,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
+      <c r="B37" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -4589,15 +4589,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="49" t="s">
+      <c r="B38" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="48"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -4605,13 +4605,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="B39" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -4619,13 +4619,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="B40" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="9"/>
       <c r="H40" s="17"/>
     </row>
@@ -4640,13 +4640,13 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>6</v>
@@ -4666,12 +4666,12 @@
         <v>52</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -4680,20 +4680,20 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -4702,20 +4702,20 @@
         <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -4730,14 +4730,14 @@
         <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H45" s="17"/>
     </row>
@@ -4752,19 +4752,40 @@
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -4777,27 +4798,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4826,50 +4826,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>242</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4881,11 +4881,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -4904,14 +4904,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4924,60 +4924,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -4989,13 +4989,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -5005,31 +5005,31 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
+      <c r="B12" s="54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="B13" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -5037,13 +5037,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="19"/>
       <c r="H14" s="17" t="s">
         <v>24</v>
@@ -5053,13 +5053,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="19"/>
       <c r="H15" s="17"/>
     </row>
@@ -5067,15 +5067,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="B16" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5083,13 +5083,13 @@
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
+      <c r="B17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="19"/>
       <c r="H17" s="17"/>
     </row>
@@ -5104,13 +5104,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G18" s="18" t="s">
         <v>6</v>
@@ -5130,12 +5130,12 @@
         <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -5144,20 +5144,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -5166,20 +5166,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -5188,20 +5188,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -5210,20 +5210,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5232,20 +5232,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -5260,14 +5260,14 @@
         <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -5275,13 +5275,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="18" t="s">
         <v>6</v>
       </c>
@@ -6309,13 +6309,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="B27" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="19"/>
       <c r="H27" s="9"/>
     </row>
@@ -6323,15 +6323,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="13"/>
@@ -7355,16 +7355,16 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="B29" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="19"/>
       <c r="H29" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
@@ -8387,15 +8387,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="B30" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="13"/>
@@ -9419,13 +9419,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
+      <c r="B31" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
       <c r="G31" s="19"/>
       <c r="H31" s="9"/>
     </row>
@@ -9433,13 +9433,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
+      <c r="B32" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
       <c r="H32" s="17"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
@@ -10469,13 +10469,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G33" s="18" t="s">
         <v>6</v>
@@ -11511,12 +11511,12 @@
         <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -11525,20 +11525,20 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -11547,20 +11547,20 @@
         <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -11569,20 +11569,20 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -11591,20 +11591,20 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -11613,20 +11613,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -11641,14 +11641,14 @@
         <v>32</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -11656,13 +11656,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="46" t="s">
+      <c r="B41" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
       <c r="G41" s="18" t="s">
         <v>6</v>
       </c>
@@ -12690,13 +12690,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
+      <c r="B42" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="19"/>
       <c r="H42" s="9"/>
     </row>
@@ -12704,15 +12704,15 @@
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
+      <c r="B43" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
       <c r="G43" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="13"/>
@@ -13736,13 +13736,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="B44" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="19"/>
       <c r="H44" s="17"/>
       <c r="I44" s="13"/>
@@ -14773,13 +14773,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G45" s="18" t="s">
         <v>6</v>
@@ -15815,12 +15815,12 @@
         <v>52</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -15835,14 +15835,14 @@
         <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H47" s="17"/>
     </row>
@@ -15850,13 +15850,13 @@
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
       <c r="G48" s="18" t="s">
         <v>6</v>
       </c>
@@ -16884,15 +16884,15 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="45" t="s">
+      <c r="B49" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="19" t="s">
         <v>205</v>
-      </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="19" t="s">
-        <v>207</v>
       </c>
       <c r="H49" s="17"/>
       <c r="I49" s="13"/>
@@ -17916,13 +17916,13 @@
       <c r="A50" s="8">
         <v>4</v>
       </c>
-      <c r="B50" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
+      <c r="B50" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
       <c r="G50" s="19"/>
       <c r="H50" s="9"/>
     </row>
@@ -17930,13 +17930,13 @@
       <c r="A51" s="8">
         <v>4</v>
       </c>
-      <c r="B51" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="B51" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
       <c r="G51" s="19"/>
       <c r="H51" s="17"/>
       <c r="I51" s="13"/>
@@ -18967,13 +18967,13 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G52" s="18" t="s">
         <v>6</v>
@@ -20009,12 +20009,12 @@
         <v>52</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -20029,19 +20029,41 @@
         <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B16:F16"/>
@@ -20058,28 +20080,6 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20108,50 +20108,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="A2" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>241</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20163,11 +20163,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -20186,14 +20186,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20206,60 +20206,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20271,13 +20271,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -20287,31 +20287,31 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
+      <c r="B12" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="B13" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -20319,13 +20319,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17" t="s">
         <v>24</v>
@@ -20335,13 +20335,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -20349,15 +20349,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
+      <c r="B16" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -20365,13 +20365,13 @@
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
+      <c r="B17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="9"/>
       <c r="H17" s="17"/>
     </row>
@@ -20386,13 +20386,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -20412,12 +20412,12 @@
         <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -20426,20 +20426,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -20448,20 +20448,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -20470,20 +20470,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -20492,20 +20492,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -20514,20 +20514,20 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -20542,14 +20542,14 @@
         <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -20557,13 +20557,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -20575,13 +20575,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="B27" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -20589,15 +20589,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="B28" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -20605,13 +20605,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="B29" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -20619,15 +20619,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="B30" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -20642,13 +20642,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -20668,12 +20668,12 @@
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -20682,20 +20682,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -20710,14 +20710,14 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -20732,14 +20732,14 @@
         <v>32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -20754,14 +20754,14 @@
         <v>32</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -20776,14 +20776,14 @@
         <v>42</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -20798,14 +20798,14 @@
         <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -20813,13 +20813,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -20831,13 +20831,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="B40" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -20845,15 +20845,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
       <c r="G41" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -20861,31 +20861,31 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H42" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
+      <c r="B43" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
@@ -20893,13 +20893,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="B44" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="9"/>
       <c r="H44" s="17"/>
     </row>
@@ -20914,13 +20914,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>6</v>
@@ -20940,12 +20940,12 @@
         <v>52</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -20954,20 +20954,20 @@
         <v>27</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H47" s="17"/>
     </row>
@@ -20982,14 +20982,14 @@
         <v>32</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -21004,14 +21004,14 @@
         <v>32</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H49" s="17"/>
     </row>
@@ -21026,14 +21026,14 @@
         <v>32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H50" s="17"/>
     </row>
@@ -21048,14 +21048,14 @@
         <v>42</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H51" s="17"/>
     </row>
@@ -21070,19 +21070,40 @@
         <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H52" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
@@ -21096,27 +21117,6 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21145,50 +21145,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>240</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21200,11 +21200,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -21223,14 +21223,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21243,60 +21243,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21308,13 +21308,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -21324,15 +21324,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
+      <c r="B12" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -21340,13 +21340,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
     </row>
@@ -21354,15 +21354,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48"/>
+      <c r="B14" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
       <c r="G14" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -21370,13 +21370,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="B15" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -21391,13 +21391,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -21417,12 +21417,12 @@
         <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -21431,20 +21431,20 @@
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -21453,20 +21453,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -21475,20 +21475,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -21497,20 +21497,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -21519,20 +21519,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -21547,14 +21547,14 @@
         <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -21562,13 +21562,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -21580,13 +21580,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="B25" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -21594,15 +21594,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H26" s="17"/>
     </row>
@@ -21610,13 +21610,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="B27" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -21624,15 +21624,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="B28" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -21647,13 +21647,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>6</v>
@@ -21673,12 +21673,12 @@
         <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -21687,20 +21687,20 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -21715,14 +21715,14 @@
         <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -21737,14 +21737,14 @@
         <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -21759,14 +21759,14 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -21774,13 +21774,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -21792,13 +21792,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
+      <c r="B36" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
     </row>
@@ -21806,15 +21806,15 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -21822,13 +21822,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="45" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
+      <c r="B38" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
@@ -21836,15 +21836,15 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="B39" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
       <c r="G39" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -21859,13 +21859,13 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>6</v>
@@ -21885,12 +21885,12 @@
         <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -21899,20 +21899,20 @@
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -21927,14 +21927,14 @@
         <v>32</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -21949,14 +21949,14 @@
         <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -21971,19 +21971,40 @@
         <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H45" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
@@ -21994,27 +22015,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22043,50 +22043,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>239</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22098,11 +22098,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -22121,14 +22121,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22141,60 +22141,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22206,13 +22206,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -22222,15 +22222,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
+      <c r="B12" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -22238,13 +22238,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
     </row>
@@ -22252,15 +22252,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48"/>
+      <c r="B14" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
       <c r="G14" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -22268,13 +22268,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="B15" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -22289,13 +22289,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -22309,20 +22309,20 @@
         <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -22331,20 +22331,20 @@
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -22353,20 +22353,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -22375,20 +22375,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -22397,20 +22397,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -22425,14 +22425,14 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -22440,13 +22440,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -22458,13 +22458,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
+      <c r="B24" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
     </row>
@@ -22472,15 +22472,15 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="B25" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -22488,13 +22488,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
+      <c r="B26" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -22502,15 +22502,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="B27" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -22525,13 +22525,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>6</v>
@@ -22551,12 +22551,12 @@
         <v>52</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -22565,20 +22565,20 @@
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -22587,20 +22587,20 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -22608,13 +22608,13 @@
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
       <c r="G32" s="1" t="s">
         <v>6</v>
       </c>
@@ -22626,13 +22626,13 @@
       <c r="A33" s="8">
         <v>3</v>
       </c>
-      <c r="B33" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
+      <c r="B33" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -22640,15 +22640,15 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
       <c r="G34" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -22656,13 +22656,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
+      <c r="B35" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -22670,15 +22670,15 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
+      <c r="B36" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="53"/>
       <c r="G36" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -22693,13 +22693,13 @@
         <v>11</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>6</v>
@@ -22719,12 +22719,12 @@
         <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -22733,20 +22733,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -22755,25 +22755,46 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B23:F23"/>
@@ -22784,27 +22805,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22833,50 +22833,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="50"/>
+      <c r="D1" s="41"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+        <v>238</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22888,11 +22888,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -22911,14 +22911,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="50"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22931,60 +22931,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22996,13 +22996,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -23012,31 +23012,31 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
+      <c r="B12" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="B13" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -23044,13 +23044,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17"/>
     </row>
@@ -23058,15 +23058,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -23074,13 +23074,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="B16" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="9"/>
       <c r="H16" s="17"/>
     </row>
@@ -23095,13 +23095,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -23121,12 +23121,12 @@
         <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -23135,20 +23135,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -23157,20 +23157,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -23179,20 +23179,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -23201,20 +23201,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -23223,20 +23223,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -23251,14 +23251,14 @@
         <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -23266,13 +23266,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -23284,13 +23284,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
+      <c r="B26" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -23298,15 +23298,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
+      <c r="B27" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -23314,13 +23314,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
+      <c r="B28" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -23328,15 +23328,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="B29" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -23351,13 +23351,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -23377,12 +23377,12 @@
         <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -23391,20 +23391,20 @@
         <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -23413,20 +23413,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -23434,13 +23434,13 @@
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B34" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -23452,13 +23452,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
+      <c r="B35" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -23466,15 +23466,15 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="45" t="s">
+      <c r="B36" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -23482,13 +23482,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
+      <c r="B37" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -23496,15 +23496,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
+      <c r="B38" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -23519,13 +23519,13 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>6</v>
@@ -23545,12 +23545,12 @@
         <v>52</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -23559,20 +23559,20 @@
         <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -23581,25 +23581,46 @@
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H42" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
@@ -23611,27 +23632,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\CSTARS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1064172-0534-42E0-85F8-B520AA5C648A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50295B5E-94B0-4C80-B52F-C0ED4F37D27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28725" yWindow="2640" windowWidth="28365" windowHeight="28305" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="323">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -209,9 +209,6 @@
   }</t>
   </si>
   <si>
-    <t>Moderate ARDS with Right Mainstem Intubation</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "Intubation": { "Type": "RightMainstem" } } }</t>
   </si>
   <si>
@@ -291,12 +288,6 @@
     <t>maj2023ventilatory</t>
   </si>
   <si>
-    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
-  </si>
-  <si>
-    <t>ShuntFraction</t>
-  </si>
-  <si>
     <t>QS/QT</t>
   </si>
   <si>
@@ -318,12 +309,6 @@
     <t>C for mild ARDS</t>
   </si>
   <si>
-    <t>VD/VT for mild ARDS</t>
-  </si>
-  <si>
-    <t>QS/QT for mild ARDS</t>
-  </si>
-  <si>
     <t>PaO2/FiO2  for mild ARDS</t>
   </si>
   <si>
@@ -339,12 +324,6 @@
     <t>C for moderate ARDS</t>
   </si>
   <si>
-    <t>VD/VT for moderate ARDS</t>
-  </si>
-  <si>
-    <t>QS/QT for moderate ARDS</t>
-  </si>
-  <si>
     <t>karbing2020changes</t>
   </si>
   <si>
@@ -375,19 +354,7 @@
     <t>C for moderate COPD</t>
   </si>
   <si>
-    <t>VD/VT for moderate COPD</t>
-  </si>
-  <si>
-    <t>QS/QT for moderate COPD</t>
-  </si>
-  <si>
     <t>C for severe ARDS</t>
-  </si>
-  <si>
-    <t>VD/VT for severe ARDS</t>
-  </si>
-  <si>
-    <t>QS/QT for severe ARDS</t>
   </si>
   <si>
     <t>PaO2/FiO2  for severe ARDS</t>
@@ -1411,6 +1378,62 @@
             "Value": 0.4
           } } } }
   }</t>
+  </si>
+  <si>
+    <t>Mild ARDS with Right Mainstem Intubation</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize mild ARDS
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>ApparentShuntFraction</t>
+  </si>
+  <si>
+    <t>ApparentPhysiologicDeadSpaceTidalVolumeRatio</t>
+  </si>
+  <si>
+    <t>VD/VT for mild ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT for mild ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>VD/VT for moderate ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT for moderate ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>VD/VT for moderate COPD (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT for moderate COPD (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>VD/VT for severe ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT for severe ARDS (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>Good:0, Fair:10</t>
   </si>
 </sst>
 </file>
@@ -1925,26 +1948,17 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1963,6 +1977,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2378,7 +2401,7 @@
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="36" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
@@ -2389,33 +2412,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="29"/>
@@ -2427,33 +2450,33 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
@@ -2465,85 +2488,85 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="33"/>
@@ -2555,7 +2578,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
@@ -2567,7 +2590,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
@@ -2579,7 +2602,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="33"/>
@@ -2591,7 +2614,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33"/>
@@ -2603,7 +2626,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
@@ -2615,7 +2638,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33"/>
@@ -2627,7 +2650,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="33"/>
@@ -2639,7 +2662,7 @@
     </row>
     <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="26" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
@@ -2651,7 +2674,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="33"/>
@@ -2663,7 +2686,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33"/>
@@ -2675,7 +2698,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="33"/>
@@ -2687,7 +2710,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29"/>
@@ -2699,7 +2722,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="33"/>
@@ -2711,7 +2734,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="25" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="33"/>
@@ -2723,7 +2746,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="25" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="33"/>
@@ -2735,7 +2758,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="25" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="33"/>
@@ -2747,7 +2770,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33"/>
@@ -2771,7 +2794,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -2783,42 +2806,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>233</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2828,13 +2851,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2846,11 +2869,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -2869,14 +2892,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -2887,8 +2910,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -2899,8 +2922,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -2908,11 +2931,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -2923,20 +2946,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2948,13 +2971,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>22</v>
@@ -2964,15 +2987,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="B12" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2980,13 +3003,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>24</v>
@@ -2996,13 +3019,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3010,15 +3033,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>160</v>
+      <c r="B15" s="39" t="s">
+        <v>149</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
       <c r="E15" s="52"/>
       <c r="F15" s="53"/>
       <c r="G15" s="9" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3026,13 +3049,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="B16" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3047,13 +3070,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3067,18 +3090,18 @@
         <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -3087,20 +3110,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -3109,20 +3132,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -3131,20 +3154,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -3153,20 +3176,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3175,20 +3198,22 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3203,14 +3228,16 @@
         <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3218,13 +3245,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -3236,13 +3263,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="B26" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -3250,15 +3277,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -3266,15 +3293,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -3282,13 +3309,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="B29" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -3296,13 +3323,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="B30" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
@@ -3317,13 +3344,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -3337,18 +3364,18 @@
         <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -3357,20 +3384,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -3379,20 +3406,20 @@
         <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -3401,20 +3428,20 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -3423,20 +3450,20 @@
         <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>89</v>
+        <v>315</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -3445,20 +3472,22 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G37" s="2" t="s">
-        <v>90</v>
+        <v>316</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -3473,14 +3502,16 @@
         <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F38" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G38" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3488,13 +3519,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -3506,13 +3537,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="B40" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -3520,15 +3551,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="40" t="s">
-        <v>199</v>
+      <c r="B41" s="39" t="s">
+        <v>188</v>
       </c>
       <c r="C41" s="52"/>
       <c r="D41" s="52"/>
       <c r="E41" s="52"/>
       <c r="F41" s="53"/>
       <c r="G41" s="9" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -3536,13 +3567,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="B42" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="9"/>
       <c r="H42" s="17"/>
     </row>
@@ -3557,13 +3588,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>6</v>
@@ -3577,18 +3608,18 @@
         <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -3603,14 +3634,14 @@
         <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H45" s="17"/>
     </row>
@@ -3619,20 +3650,20 @@
         <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -3640,13 +3671,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -3658,15 +3689,15 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="40" t="s">
-        <v>201</v>
+      <c r="B48" s="39" t="s">
+        <v>190</v>
       </c>
       <c r="C48" s="52"/>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
       <c r="F48" s="53"/>
       <c r="G48" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -3674,13 +3705,13 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="B49" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
@@ -3689,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
@@ -3709,13 +3740,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3729,18 +3760,18 @@
         <v>37</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H52" s="17"/>
     </row>
@@ -3749,20 +3780,20 @@
         <v>27</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -3777,14 +3808,14 @@
         <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54" s="17"/>
     </row>
@@ -3799,14 +3830,14 @@
         <v>32</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55" s="17"/>
     </row>
@@ -3821,14 +3852,14 @@
         <v>32</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H56" s="17"/>
     </row>
@@ -3837,20 +3868,20 @@
         <v>27</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>75</v>
+        <v>317</v>
       </c>
       <c r="H57" s="17"/>
     </row>
@@ -3871,6 +3902,7 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -3882,7 +3914,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="G5:H5"/>
@@ -3908,7 +3939,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" style="11" bestFit="1" customWidth="1"/>
@@ -3920,40 +3951,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>232</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -3961,13 +3992,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3979,11 +4010,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -4002,14 +4033,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4026,8 +4057,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -4038,8 +4069,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -4047,11 +4078,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -4062,20 +4093,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4087,13 +4118,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -4103,15 +4134,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="B12" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -4119,13 +4150,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
     </row>
@@ -4133,13 +4164,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17"/>
     </row>
@@ -4147,15 +4178,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="B15" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -4163,13 +4194,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="B16" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="9"/>
       <c r="H16" s="17"/>
     </row>
@@ -4184,13 +4215,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4204,18 +4235,18 @@
         <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -4224,20 +4255,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -4246,20 +4277,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -4268,20 +4299,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -4290,20 +4321,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4312,20 +4343,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>319</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -4333,13 +4364,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4351,13 +4382,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="B25" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -4365,15 +4396,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="B26" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="9" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -4395,13 +4426,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -4409,13 +4440,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="B29" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="9"/>
       <c r="H29" s="17"/>
     </row>
@@ -4430,13 +4461,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -4450,18 +4481,18 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -4470,20 +4501,20 @@
         <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -4492,20 +4523,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -4520,14 +4551,14 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -4542,14 +4573,14 @@
         <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -4557,13 +4588,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4575,13 +4606,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -4597,7 +4628,7 @@
       <c r="E38" s="52"/>
       <c r="F38" s="53"/>
       <c r="G38" s="9" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -4605,13 +4636,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+      <c r="B39" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -4619,13 +4650,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="B40" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="9"/>
       <c r="H40" s="17"/>
     </row>
@@ -4640,13 +4671,13 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>6</v>
@@ -4660,18 +4691,18 @@
         <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -4680,20 +4711,20 @@
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -4702,20 +4733,20 @@
         <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -4730,14 +4761,14 @@
         <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H45" s="17"/>
     </row>
@@ -4752,14 +4783,14 @@
         <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -4814,7 +4845,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -4826,50 +4857,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>231</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4881,11 +4912,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -4904,14 +4935,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4928,8 +4959,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -4940,8 +4971,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -4949,11 +4980,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -4964,20 +4995,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -5006,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -5014,22 +5045,22 @@
       <c r="F12" s="53"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="B13" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="19" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -5037,13 +5068,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="19"/>
       <c r="H14" s="17" t="s">
         <v>24</v>
@@ -5053,13 +5084,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="19"/>
       <c r="H15" s="17"/>
     </row>
@@ -5067,15 +5098,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="B16" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="19" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -5083,13 +5114,13 @@
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="B17" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="19"/>
       <c r="H17" s="17"/>
     </row>
@@ -5104,13 +5135,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G18" s="18" t="s">
         <v>6</v>
@@ -5124,18 +5155,18 @@
         <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -5144,20 +5175,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -5166,20 +5197,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -5188,20 +5219,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -5210,20 +5241,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="21" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5232,20 +5263,22 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G24" s="20" t="s">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -5260,14 +5293,16 @@
         <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G25" s="20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -5275,13 +5310,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="18" t="s">
         <v>6</v>
       </c>
@@ -6309,13 +6344,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="19"/>
       <c r="H27" s="9"/>
     </row>
@@ -6323,15 +6358,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="19" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="13"/>
@@ -7355,16 +7390,16 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="B29" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="19"/>
       <c r="H29" s="17" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
@@ -8387,15 +8422,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="B30" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
       <c r="G30" s="19" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="H30" s="17"/>
       <c r="I30" s="13"/>
@@ -9419,13 +9454,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
+      <c r="B31" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
       <c r="G31" s="19"/>
       <c r="H31" s="9"/>
     </row>
@@ -9433,13 +9468,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
+      <c r="B32" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
       <c r="H32" s="17"/>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
@@ -10469,13 +10504,13 @@
         <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G33" s="18" t="s">
         <v>6</v>
@@ -11505,18 +11540,18 @@
         <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -11525,20 +11560,20 @@
         <v>27</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="21" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -11547,20 +11582,20 @@
         <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="21" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -11569,20 +11604,20 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -11591,20 +11626,20 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="21" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -11613,20 +11648,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="20" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -11641,14 +11676,14 @@
         <v>32</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -11656,13 +11691,13 @@
       <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="18" t="s">
         <v>6</v>
       </c>
@@ -12690,13 +12725,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="B42" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="19"/>
       <c r="H42" s="9"/>
     </row>
@@ -12704,15 +12739,15 @@
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="B43" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
       <c r="G43" s="19" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="13"/>
@@ -13736,13 +13771,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
+      <c r="B44" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="19"/>
       <c r="H44" s="17"/>
       <c r="I44" s="13"/>
@@ -14773,13 +14808,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G45" s="18" t="s">
         <v>6</v>
@@ -15809,18 +15844,18 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -15835,14 +15870,14 @@
         <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H47" s="17"/>
     </row>
@@ -15850,13 +15885,13 @@
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
       <c r="G48" s="18" t="s">
         <v>6</v>
       </c>
@@ -16884,15 +16919,15 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
+      <c r="B49" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="19" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H49" s="17"/>
       <c r="I49" s="13"/>
@@ -17916,13 +17951,13 @@
       <c r="A50" s="8">
         <v>4</v>
       </c>
-      <c r="B50" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
+      <c r="B50" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
       <c r="G50" s="19"/>
       <c r="H50" s="9"/>
     </row>
@@ -17930,13 +17965,13 @@
       <c r="A51" s="8">
         <v>4</v>
       </c>
-      <c r="B51" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
+      <c r="B51" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
       <c r="G51" s="19"/>
       <c r="H51" s="17"/>
       <c r="I51" s="13"/>
@@ -18967,13 +19002,13 @@
         <v>11</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G52" s="18" t="s">
         <v>6</v>
@@ -20003,18 +20038,18 @@
         <v>37</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H53" s="17"/>
     </row>
@@ -20029,14 +20064,14 @@
         <v>32</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H54" s="17"/>
     </row>
@@ -20096,7 +20131,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -20108,50 +20143,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>230</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20163,11 +20198,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -20186,14 +20221,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20210,8 +20245,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -20222,8 +20257,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -20231,11 +20266,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -20246,20 +20281,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20271,13 +20306,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -20288,7 +20323,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -20296,22 +20331,22 @@
       <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="B13" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -20319,13 +20354,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17" t="s">
         <v>24</v>
@@ -20335,13 +20370,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -20349,15 +20384,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>188</v>
+      <c r="B16" s="39" t="s">
+        <v>177</v>
       </c>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
       <c r="F16" s="53"/>
       <c r="G16" s="9" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -20365,13 +20400,13 @@
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="B17" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="9"/>
       <c r="H17" s="17"/>
     </row>
@@ -20386,13 +20421,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>6</v>
@@ -20406,18 +20441,18 @@
         <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -20426,20 +20461,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -20448,20 +20483,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -20470,20 +20505,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -20492,20 +20527,20 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>89</v>
+        <v>315</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -20514,20 +20549,22 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>316</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -20542,14 +20579,16 @@
         <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -20557,13 +20596,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -20575,13 +20614,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -20589,15 +20628,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -20605,13 +20644,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="B29" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -20619,15 +20658,15 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="B30" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
       <c r="G30" s="9" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -20642,13 +20681,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>6</v>
@@ -20662,18 +20701,18 @@
         <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -20682,20 +20721,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -20710,14 +20749,14 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -20732,14 +20771,14 @@
         <v>32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H35" s="17"/>
     </row>
@@ -20754,14 +20793,14 @@
         <v>32</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -20776,14 +20815,14 @@
         <v>42</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -20798,14 +20837,14 @@
         <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -20813,13 +20852,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -20831,13 +20870,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="B40" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -20845,15 +20884,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
       <c r="G41" s="9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -20861,31 +20900,31 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="B42" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="9" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>3</v>
       </c>
-      <c r="B43" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="B43" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
@@ -20893,13 +20932,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
+      <c r="B44" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="9"/>
       <c r="H44" s="17"/>
     </row>
@@ -20914,13 +20953,13 @@
         <v>11</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>6</v>
@@ -20934,18 +20973,18 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H46" s="17"/>
     </row>
@@ -20954,20 +20993,20 @@
         <v>27</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H47" s="17"/>
     </row>
@@ -20982,14 +21021,14 @@
         <v>32</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H48" s="17"/>
     </row>
@@ -21004,14 +21043,14 @@
         <v>32</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H49" s="17"/>
     </row>
@@ -21026,14 +21065,14 @@
         <v>32</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H50" s="17"/>
     </row>
@@ -21048,14 +21087,14 @@
         <v>42</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H51" s="17"/>
     </row>
@@ -21070,14 +21109,14 @@
         <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H52" s="17"/>
     </row>
@@ -21133,7 +21172,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -21145,50 +21184,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>229</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21200,11 +21239,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -21223,14 +21262,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21247,8 +21286,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -21259,8 +21298,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -21268,11 +21307,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -21283,20 +21322,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21308,13 +21347,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -21324,15 +21363,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="B12" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -21340,13 +21379,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="17"/>
     </row>
@@ -21354,15 +21393,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
-        <v>162</v>
+      <c r="B14" s="39" t="s">
+        <v>151</v>
       </c>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="52"/>
       <c r="F14" s="53"/>
       <c r="G14" s="9" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -21370,13 +21409,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="B15" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -21391,13 +21430,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -21411,18 +21450,18 @@
         <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -21431,20 +21470,20 @@
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -21453,20 +21492,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -21475,20 +21514,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -21497,20 +21536,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>89</v>
+        <v>313</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -21519,20 +21558,22 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>314</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -21547,14 +21588,16 @@
         <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -21562,13 +21605,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -21580,13 +21623,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="B25" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -21594,15 +21637,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="B26" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="9" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H26" s="17"/>
     </row>
@@ -21610,13 +21653,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -21624,15 +21667,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="9" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="H28" s="17"/>
     </row>
@@ -21647,13 +21690,13 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>6</v>
@@ -21667,18 +21710,18 @@
         <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -21687,20 +21730,20 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -21715,14 +21758,14 @@
         <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -21737,14 +21780,14 @@
         <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -21759,14 +21802,14 @@
         <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -21774,13 +21817,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -21792,13 +21835,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="B36" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
     </row>
@@ -21806,15 +21849,15 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
       <c r="G37" s="9" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -21822,13 +21865,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="B38" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
@@ -21836,15 +21879,15 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+      <c r="B39" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="9" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -21859,13 +21902,13 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>6</v>
@@ -21879,18 +21922,18 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -21899,20 +21942,20 @@
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H42" s="17"/>
     </row>
@@ -21927,14 +21970,14 @@
         <v>32</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H43" s="17"/>
     </row>
@@ -21949,14 +21992,14 @@
         <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H44" s="17"/>
     </row>
@@ -21971,14 +22014,14 @@
         <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H45" s="17"/>
     </row>
@@ -22031,7 +22074,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -22043,50 +22086,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>228</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22098,11 +22141,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="17" t="s">
         <v>8</v>
@@ -22121,14 +22164,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22145,8 +22188,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -22157,8 +22200,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -22166,11 +22209,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -22181,20 +22224,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22206,13 +22249,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -22222,15 +22265,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
+      <c r="B12" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="9" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H12" s="17"/>
     </row>
@@ -22238,13 +22281,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
     </row>
@@ -22253,14 +22296,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="52"/>
       <c r="F14" s="53"/>
       <c r="G14" s="9" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="H14" s="17"/>
     </row>
@@ -22268,13 +22311,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="B15" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="9"/>
       <c r="H15" s="17"/>
     </row>
@@ -22289,13 +22332,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>6</v>
@@ -22309,20 +22352,20 @@
         <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H17" s="17"/>
     </row>
@@ -22331,20 +22374,20 @@
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -22353,20 +22396,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -22375,20 +22418,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>89</v>
+        <v>315</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -22397,20 +22440,22 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F21" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>316</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -22425,14 +22470,16 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -22440,13 +22487,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -22458,13 +22505,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="B24" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
     </row>
@@ -22472,15 +22519,15 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>318</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="B25" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="9" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -22488,13 +22535,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="B26" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -22502,15 +22549,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="9" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -22525,13 +22572,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>6</v>
@@ -22545,18 +22592,18 @@
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -22565,20 +22612,20 @@
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H30" s="17"/>
     </row>
@@ -22587,20 +22634,20 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -22608,13 +22655,13 @@
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="1" t="s">
         <v>6</v>
       </c>
@@ -22626,13 +22673,13 @@
       <c r="A33" s="8">
         <v>3</v>
       </c>
-      <c r="B33" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
+      <c r="B33" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -22640,15 +22687,15 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="B34" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
       <c r="G34" s="9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H34" s="17"/>
     </row>
@@ -22656,13 +22703,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="B35" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -22671,14 +22718,14 @@
         <v>3</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="52"/>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
       <c r="F36" s="53"/>
       <c r="G36" s="9" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -22693,13 +22740,13 @@
         <v>11</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>6</v>
@@ -22713,18 +22760,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -22733,20 +22780,20 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -22755,20 +22802,20 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -22821,7 +22868,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="46" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -22833,50 +22880,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="41"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="A2" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+        <v>227</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22888,11 +22935,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -22911,14 +22958,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="41"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22935,8 +22982,8 @@
         <v>17</v>
       </c>
       <c r="F6" s="42"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
@@ -22947,8 +22994,8 @@
         <v>18</v>
       </c>
       <c r="F7" s="42"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -22956,11 +23003,11 @@
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
       <c r="E8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="42"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -22971,20 +23018,20 @@
         <v>19</v>
       </c>
       <c r="F9" s="42"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22996,13 +23043,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -23013,7 +23060,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
@@ -23021,22 +23068,22 @@
       <c r="F12" s="53"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="B13" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="9" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H13" s="17"/>
     </row>
@@ -23044,13 +23091,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="17"/>
     </row>
@@ -23058,15 +23105,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="B15" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="9" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -23074,13 +23121,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="B16" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="9"/>
       <c r="H16" s="17"/>
     </row>
@@ -23095,13 +23142,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -23115,18 +23162,18 @@
         <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H18" s="17"/>
     </row>
@@ -23135,20 +23182,20 @@
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H19" s="17"/>
     </row>
@@ -23157,20 +23204,20 @@
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -23179,20 +23226,20 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -23201,20 +23248,20 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -23223,20 +23270,22 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="10"/>
+        <v>162</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -23251,14 +23300,16 @@
         <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>322</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -23266,13 +23317,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -23284,13 +23335,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
+      <c r="B26" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -23298,15 +23349,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="B27" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="9" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H27" s="17"/>
     </row>
@@ -23314,13 +23365,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -23328,15 +23379,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
+      <c r="B29" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H29" s="17"/>
     </row>
@@ -23351,13 +23402,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>6</v>
@@ -23371,18 +23422,18 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H31" s="17"/>
     </row>
@@ -23391,20 +23442,20 @@
         <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="17"/>
     </row>
@@ -23413,20 +23464,20 @@
         <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33" s="17"/>
     </row>
@@ -23434,13 +23485,13 @@
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
@@ -23452,13 +23503,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="B35" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
     </row>
@@ -23466,15 +23517,15 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="B36" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
       <c r="G36" s="9" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -23482,13 +23533,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
+      <c r="B37" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -23496,15 +23547,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="B38" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
       <c r="G38" s="9" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -23519,13 +23570,13 @@
         <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>6</v>
@@ -23539,18 +23590,18 @@
         <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -23559,20 +23610,20 @@
         <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="17"/>
     </row>
@@ -23581,20 +23632,20 @@
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H42" s="17"/>
     </row>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50295B5E-94B0-4C80-B52F-C0ED4F37D27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7678C5D6-5C86-46C0-B2FF-1C550A10A9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28725" yWindow="2640" windowWidth="28365" windowHeight="28305" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\CSTARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC4A6A2-14D3-46AE-A505-AFAB17A0F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96BB453-B3BC-40FF-8BCA-FAFBFF6AD250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28170" yWindow="3435" windowWidth="29445" windowHeight="26775" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21705" yWindow="2100" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="8" r:id="rId1"/>
@@ -1168,34 +1168,16 @@
 &lt;br /&gt;</t>
   </si>
   <si>
-    <t>ApparentShuntFraction</t>
-  </si>
-  <si>
-    <t>ApparentPhysiologicDeadSpaceTidalVolumeRatio</t>
-  </si>
-  <si>
-    <t>VD/VT for mild ARDS (determined from blood gas values)</t>
-  </si>
-  <si>
     <t>QS/QT for mild ARDS (determined from blood gas values)</t>
   </si>
   <si>
-    <t>VD/VT for moderate ARDS (determined from blood gas values)</t>
-  </si>
-  <si>
     <t>QS/QT for moderate ARDS (determined from blood gas values)</t>
   </si>
   <si>
     <t>QS/QT (determined from blood gas values)</t>
   </si>
   <si>
-    <t>VD/VT for moderate COPD (determined from blood gas values)</t>
-  </si>
-  <si>
     <t>QS/QT for moderate COPD (determined from blood gas values)</t>
-  </si>
-  <si>
-    <t>VD/VT for severe ARDS (determined from blood gas values)</t>
   </si>
   <si>
     <t>QS/QT for severe ARDS (determined from blood gas values)</t>
@@ -1439,6 +1421,24 @@
   "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
   }}
 }</t>
+  </si>
+  <si>
+    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
+  </si>
+  <si>
+    <t>VD/VT for mild ARDS</t>
+  </si>
+  <si>
+    <t>VD/VT for moderate ARDS</t>
+  </si>
+  <si>
+    <t>VD/VT for moderate COPD</t>
+  </si>
+  <si>
+    <t>VD/VT for severe ARDS</t>
+  </si>
+  <si>
+    <t>ClinicalShuntFraction</t>
   </si>
 </sst>
 </file>
@@ -1957,10 +1957,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1982,24 +2000,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2811,42 +2811,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="AMG1" s="13"/>
       <c r="AMH1" s="13"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
       <c r="AMG2" s="13"/>
       <c r="AMH2" s="13"/>
       <c r="AMI2" s="13"/>
@@ -2856,13 +2856,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2897,74 +2897,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -3017,7 +3017,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3057,10 +3057,10 @@
       <c r="B16" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="53"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="9" t="s">
         <v>114</v>
       </c>
@@ -3181,14 +3181,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -3197,7 +3197,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -3219,7 +3219,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -3262,13 +3262,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -3327,7 +3327,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -3335,7 +3335,7 @@
       <c r="F30" s="39"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H36" s="17"/>
     </row>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>28</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="H37" s="17"/>
     </row>
@@ -3491,7 +3491,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>28</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -3534,13 +3534,13 @@
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -3569,10 +3569,10 @@
       <c r="B42" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="53"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="42"/>
       <c r="G42" s="9" t="s">
         <v>145</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>27</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>28</v>
@@ -3686,13 +3686,13 @@
       <c r="A48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="41" t="s">
+      <c r="B48" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
       <c r="G48" s="1" t="s">
         <v>6</v>
       </c>
@@ -3707,10 +3707,10 @@
       <c r="B49" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="53"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="42"/>
       <c r="G49" s="9" t="s">
         <v>147</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C50" s="39"/>
       <c r="D50" s="39"/>
@@ -3734,13 +3734,13 @@
       <c r="A51" s="8">
         <v>4</v>
       </c>
-      <c r="B51" s="54" t="s">
+      <c r="B51" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="53"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="42"/>
       <c r="G51" s="9"/>
       <c r="H51" s="17"/>
     </row>
@@ -3883,7 +3883,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>28</v>
@@ -3896,12 +3896,33 @@
       </c>
       <c r="F58" s="10"/>
       <c r="G58" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H58" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
@@ -3918,27 +3939,6 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3967,40 +3967,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
       <c r="AMI1" s="13"/>
       <c r="AMJ1" s="13"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
       <c r="AMI2" s="13"/>
       <c r="AMJ2" s="13"/>
     </row>
@@ -4008,13 +4008,13 @@
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4049,14 +4049,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4069,60 +4069,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -4337,7 +4337,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>268</v>
+        <v>316</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -4359,7 +4359,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -4380,13 +4380,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -4413,7 +4413,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -4443,7 +4443,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -4604,13 +4604,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -4636,13 +4636,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="42"/>
       <c r="G38" s="9" t="s">
         <v>152</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -4812,27 +4812,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -4845,6 +4824,27 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4873,50 +4873,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4951,14 +4951,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4971,60 +4971,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="18" t="s">
         <v>6</v>
       </c>
@@ -5036,13 +5036,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="42"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17" t="s">
         <v>22</v>
@@ -5052,13 +5052,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -5069,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -5085,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -5093,7 +5093,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5257,14 +5257,14 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -5273,7 +5273,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="21" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -5295,7 +5295,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -5338,13 +5338,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="18" t="s">
         <v>6</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -8451,7 +8451,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
@@ -9483,7 +9483,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
@@ -9491,7 +9491,7 @@
       <c r="F32" s="39"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:1024" x14ac:dyDescent="0.2">
@@ -11640,14 +11640,14 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H38" s="17"/>
     </row>
@@ -11656,7 +11656,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="21" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="H39" s="17"/>
     </row>
@@ -11678,7 +11678,7 @@
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>28</v>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="20" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H40" s="17"/>
     </row>
@@ -11721,13 +11721,13 @@
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="18" t="s">
         <v>6</v>
       </c>
@@ -12756,7 +12756,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
@@ -15915,13 +15915,13 @@
       <c r="A49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="41" t="s">
+      <c r="B49" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
       <c r="G49" s="18" t="s">
         <v>6</v>
       </c>
@@ -17982,7 +17982,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C51" s="39"/>
       <c r="D51" s="39"/>
@@ -20107,29 +20107,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B17:F17"/>
@@ -20146,6 +20123,29 @@
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20174,50 +20174,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -20252,14 +20252,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -20272,60 +20272,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -20353,13 +20353,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -20386,7 +20386,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -20394,7 +20394,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20434,10 +20434,10 @@
       <c r="B17" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="9" t="s">
         <v>134</v>
       </c>
@@ -20565,7 +20565,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -20574,7 +20574,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="12" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -20596,7 +20596,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>28</v>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H25" s="17"/>
     </row>
@@ -20639,13 +20639,13 @@
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
       <c r="G27" s="1" t="s">
         <v>6</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -20688,7 +20688,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -20858,7 +20858,7 @@
         <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>29</v>
@@ -20880,7 +20880,7 @@
         <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>29</v>
@@ -20895,13 +20895,13 @@
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
@@ -20914,7 +20914,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
@@ -20962,7 +20962,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C44" s="39"/>
       <c r="D44" s="39"/>
@@ -21130,7 +21130,7 @@
         <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>29</v>
@@ -21152,7 +21152,7 @@
         <v>42</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>29</v>
@@ -21165,28 +21165,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B45:F45"/>
@@ -21200,6 +21178,28 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -21228,50 +21228,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -21306,14 +21306,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -21326,60 +21326,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -21432,7 +21432,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -21454,14 +21454,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
+        <v>309</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="H15" s="17"/>
     </row>
@@ -21580,14 +21580,14 @@
         <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -21618,7 +21618,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -21661,13 +21661,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -21680,7 +21680,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -21710,7 +21710,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -21873,13 +21873,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -21922,7 +21922,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C39" s="39"/>
       <c r="D39" s="39"/>
@@ -22083,28 +22083,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
@@ -22115,6 +22093,28 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22143,50 +22143,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -22221,14 +22221,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -22241,60 +22241,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -22323,7 +22323,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -22339,7 +22339,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
@@ -22347,7 +22347,7 @@
       <c r="F13" s="39"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22368,13 +22368,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="9" t="s">
         <v>158</v>
       </c>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H20" s="17"/>
     </row>
@@ -22491,7 +22491,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
@@ -22504,7 +22504,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="H21" s="17"/>
     </row>
@@ -22513,7 +22513,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>28</v>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -22556,13 +22556,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -22575,7 +22575,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -22605,7 +22605,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -22724,13 +22724,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -22743,7 +22743,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
@@ -22773,7 +22773,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -22786,13 +22786,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="53"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="42"/>
       <c r="G37" s="9" t="s">
         <v>119</v>
       </c>
@@ -22890,28 +22890,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
@@ -22922,6 +22900,28 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22950,50 +22950,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -23028,14 +23028,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="44" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -23048,60 +23048,60 @@
         <v>16</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -23129,13 +23129,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="s">
         <v>125</v>
@@ -23162,7 +23162,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
@@ -23170,7 +23170,7 @@
       <c r="F14" s="39"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -23192,14 +23192,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H16" s="17"/>
     </row>
@@ -23318,14 +23318,14 @@
         <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H22" s="17"/>
     </row>
@@ -23334,7 +23334,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>28</v>
@@ -23347,7 +23347,7 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="H23" s="17"/>
     </row>
@@ -23356,7 +23356,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -23369,7 +23369,7 @@
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H24" s="17"/>
     </row>
@@ -23399,13 +23399,13 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="1" t="s">
         <v>6</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -23448,7 +23448,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
@@ -23462,7 +23462,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
@@ -23567,13 +23567,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -23586,7 +23586,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C36" s="39"/>
       <c r="D36" s="39"/>
@@ -23616,7 +23616,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C38" s="39"/>
       <c r="D38" s="39"/>
@@ -23733,28 +23733,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:F39"/>
@@ -23766,6 +23744,28 @@
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
